--- a/diseases/d145/2026-2029.xlsx
+++ b/diseases/d145/2026-2029.xlsx
@@ -6701,6 +6701,151 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>D145</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>relapsing-fever</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Relapsing fever</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>D145</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Relapsing fever</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>回归热</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP43" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr"/>
+      <c r="AT43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV43" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA43" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB43" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC43" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6734,7 +6879,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -6817,7 +6962,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10">
@@ -6827,7 +6972,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d145/2026-2029.xlsx
+++ b/diseases/d145/2026-2029.xlsx
@@ -6846,6 +6846,151 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>D145</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>relapsing-fever</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Relapsing fever</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>D145</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Relapsing fever</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>回归热</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP44" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr"/>
+      <c r="AT44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV44" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA44" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB44" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC44" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6879,7 +7024,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -6962,7 +7107,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10">
@@ -6972,7 +7117,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d145/2026-2029.xlsx
+++ b/diseases/d145/2026-2029.xlsx
@@ -6149,12 +6149,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -6179,7 +6179,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -6227,42 +6227,42 @@
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC39" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -6904,12 +6904,12 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -6986,6 +6986,296 @@
         </is>
       </c>
       <c r="BC44" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>D145</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>relapsing-fever</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Relapsing fever</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>D145</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Relapsing fever</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>回归热</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP45" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr"/>
+      <c r="AT45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV45" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA45" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB45" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC45" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>D145</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>relapsing-fever</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Relapsing fever</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>D145</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Relapsing fever</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>回归热</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP46" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr"/>
+      <c r="AT46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV46" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA46" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB46" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC46" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -7024,7 +7314,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -7107,7 +7397,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10">
@@ -7117,7 +7407,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d145/2026-2029.xlsx
+++ b/diseases/d145/2026-2029.xlsx
@@ -7281,6 +7281,151 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>D145</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>relapsing-fever</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Relapsing fever</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>D145</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Relapsing fever</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>回归热</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP47" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr"/>
+      <c r="AT47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV47" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA47" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB47" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC47" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7314,7 +7459,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -7397,7 +7542,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10">
@@ -7407,7 +7552,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d145/2026-2029.xlsx
+++ b/diseases/d145/2026-2029.xlsx
@@ -7426,6 +7426,151 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>D145</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>relapsing-fever</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Relapsing fever</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>D145</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Relapsing fever</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>回归热</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP48" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr"/>
+      <c r="AT48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV48" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA48" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB48" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC48" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7459,7 +7604,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -7542,7 +7687,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10">
@@ -7552,7 +7697,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d145/2026-2029.xlsx
+++ b/diseases/d145/2026-2029.xlsx
@@ -773,6 +773,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1510,6 +1515,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2247,6 +2257,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2984,6 +2999,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3721,6 +3741,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4606,6 +4631,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5331,6 +5361,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6199,6 +6234,11 @@
       <c r="S39" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">

--- a/diseases/d145/2026-2029.xlsx
+++ b/diseases/d145/2026-2029.xlsx
@@ -7611,6 +7611,151 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>D145</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>relapsing-fever</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Relapsing fever</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>D145</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Relapsing fever</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>回归热</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP49" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr"/>
+      <c r="AT49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV49" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA49" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB49" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC49" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7644,7 +7789,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7872,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10">
@@ -7737,7 +7882,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11">
